--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2080" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C9CAFA1-ECC5-4B00-A53E-970CC5A07938}"/>
+  <xr:revisionPtr revIDLastSave="2088" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BBE35EF-00F8-4FE2-969D-B7BAF9B5FC1D}"/>
   <bookViews>
-    <workbookView xWindow="14028" yWindow="2052" windowWidth="8904" windowHeight="10116" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14496" yWindow="900" windowWidth="8340" windowHeight="10776" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="110">
   <si>
     <t>Market</t>
   </si>
@@ -492,6 +492,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:F349"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -6667,6 +6671,73 @@
         <v>1</v>
       </c>
     </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="10">
+        <v>46052</v>
+      </c>
+      <c r="B344" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C344" s="10"/>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="6">
+        <v>2</v>
+      </c>
+      <c r="B345" s="8">
+        <v>3547260</v>
+      </c>
+      <c r="C345" s="7">
+        <f>B345/B349</f>
+        <v>0.55218222078665025</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="6">
+        <v>3</v>
+      </c>
+      <c r="B346" s="8">
+        <v>1978055</v>
+      </c>
+      <c r="C346" s="7">
+        <f>B346/B349</f>
+        <v>0.30791281235041623</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="6">
+        <v>4</v>
+      </c>
+      <c r="B347" s="8">
+        <v>740240</v>
+      </c>
+      <c r="C347" s="7">
+        <f>B347/B349</f>
+        <v>0.11522904075684048</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="6">
+        <v>1</v>
+      </c>
+      <c r="B348" s="8">
+        <v>158520</v>
+      </c>
+      <c r="C348" s="7">
+        <f>B348/B349</f>
+        <v>2.4675926106093093E-2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="B349" s="9">
+        <f>SUM(B345:B348)</f>
+        <v>6424075</v>
+      </c>
+      <c r="C349" s="7">
+        <f>SUM(C345:C348)</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6674,7 +6745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -9035,6 +9106,37 @@
         <v>10770840</v>
       </c>
     </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="43.2">
+      <c r="A170" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="5"/>
+      <c r="B171" s="4">
+        <v>-948000</v>
+      </c>
+      <c r="C171" s="13">
+        <v>10770840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2088" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BBE35EF-00F8-4FE2-969D-B7BAF9B5FC1D}"/>
+  <xr:revisionPtr revIDLastSave="2104" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9CADA62-DE50-4E41-93F5-90EF67E77298}"/>
   <bookViews>
-    <workbookView xWindow="14496" yWindow="900" windowWidth="8340" windowHeight="10776" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14196" yWindow="828" windowWidth="8844" windowHeight="11784" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="111">
   <si>
     <t>Market</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>-1.33, 59.85, 41.48</t>
+  </si>
+  <si>
+    <t>18.17, 19.19, 62.64</t>
   </si>
 </sst>
 </file>
@@ -492,10 +495,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6679,6 +6678,13 @@
         <v>1</v>
       </c>
       <c r="C344" s="10"/>
+      <c r="D344" s="10">
+        <v>46080</v>
+      </c>
+      <c r="E344" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F344" s="10"/>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="6">
@@ -6691,6 +6697,16 @@
         <f>B345/B349</f>
         <v>0.55218222078665025</v>
       </c>
+      <c r="D345" s="6">
+        <v>2</v>
+      </c>
+      <c r="E345" s="8">
+        <v>4592190</v>
+      </c>
+      <c r="F345" s="7">
+        <f>E345/E349</f>
+        <v>0.65861928016694271</v>
+      </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="6">
@@ -6703,6 +6719,16 @@
         <f>B346/B349</f>
         <v>0.30791281235041623</v>
       </c>
+      <c r="D346" s="6">
+        <v>3</v>
+      </c>
+      <c r="E346" s="8">
+        <v>1489800</v>
+      </c>
+      <c r="F346" s="7">
+        <f>E346/E349</f>
+        <v>0.21366951358561195</v>
+      </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="6">
@@ -6715,6 +6741,16 @@
         <f>B347/B349</f>
         <v>0.11522904075684048</v>
       </c>
+      <c r="D347" s="6">
+        <v>1</v>
+      </c>
+      <c r="E347" s="8">
+        <v>487500</v>
+      </c>
+      <c r="F347" s="7">
+        <f>E347/E349</f>
+        <v>6.9918034550265684E-2</v>
+      </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="6">
@@ -6726,6 +6762,16 @@
       <c r="C348" s="7">
         <f>B348/B349</f>
         <v>2.4675926106093093E-2</v>
+      </c>
+      <c r="D348" s="6">
+        <v>4</v>
+      </c>
+      <c r="E348" s="8">
+        <v>402960</v>
+      </c>
+      <c r="F348" s="7">
+        <f>E348/E349</f>
+        <v>5.7793171697179617E-2</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -6736,6 +6782,14 @@
       <c r="C349" s="7">
         <f>SUM(C345:C348)</f>
         <v>1</v>
+      </c>
+      <c r="E349" s="9">
+        <f>SUM(E345:E348)</f>
+        <v>6972450</v>
+      </c>
+      <c r="F349" s="7">
+        <f>SUM(F345:F348)</f>
+        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>
@@ -9116,25 +9170,50 @@
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D169" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="170" spans="1:6" ht="43.2">
       <c r="A170" s="2">
         <v>46052</v>
       </c>
-      <c r="B170" s="3" t="s">
-        <v>109</v>
+      <c r="B170" s="3">
+        <v>0</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>108</v>
+      </c>
+      <c r="D170" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E170" s="3">
+        <v>0</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="5"/>
       <c r="B171" s="4">
-        <v>-948000</v>
+        <v>0</v>
       </c>
       <c r="C171" s="13">
         <v>10770840</v>
+      </c>
+      <c r="D171" s="5"/>
+      <c r="E171" s="4">
+        <v>0</v>
+      </c>
+      <c r="F171" s="13">
+        <v>10808840</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2104" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9CADA62-DE50-4E41-93F5-90EF67E77298}"/>
+  <xr:revisionPtr revIDLastSave="2118" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66061B69-FD50-4283-9332-66A9BC3ABADC}"/>
   <bookViews>
-    <workbookView xWindow="14196" yWindow="828" windowWidth="8844" windowHeight="11784" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14364" yWindow="1356" windowWidth="8676" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="113">
   <si>
     <t>Market</t>
   </si>
@@ -370,6 +370,12 @@
   </si>
   <si>
     <t>18.17, 19.19, 62.64</t>
+  </si>
+  <si>
+    <t>14.68, 20.34, 64.97</t>
+  </si>
+  <si>
+    <t>102.8, -0.0, -2.8</t>
   </si>
 </sst>
 </file>
@@ -794,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F349"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -6792,6 +6798,73 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B351" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C351" s="10"/>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="6">
+        <v>2</v>
+      </c>
+      <c r="B352" s="8">
+        <v>4300660</v>
+      </c>
+      <c r="C352" s="7">
+        <f>B352/B356</f>
+        <v>0.66215495281330328</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="6">
+        <v>3</v>
+      </c>
+      <c r="B353" s="8">
+        <v>1477025</v>
+      </c>
+      <c r="C353" s="7">
+        <f>B353/B356</f>
+        <v>0.22741147153671049</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="6">
+        <v>1</v>
+      </c>
+      <c r="B354" s="8">
+        <v>404160</v>
+      </c>
+      <c r="C354" s="7">
+        <f>B354/B356</f>
+        <v>6.2226854884837361E-2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="6">
+        <v>4</v>
+      </c>
+      <c r="B355" s="8">
+        <v>313100</v>
+      </c>
+      <c r="C355" s="7">
+        <f>B355/B356</f>
+        <v>4.8206720765148897E-2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="B356" s="9">
+        <f>SUM(B352:B355)</f>
+        <v>6494945</v>
+      </c>
+      <c r="C356" s="7">
+        <f>SUM(C352:C355)</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6799,7 +6872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -9216,6 +9289,37 @@
         <v>10808840</v>
       </c>
     </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="43.2">
+      <c r="A174" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="5"/>
+      <c r="B175" s="4">
+        <v>-315150</v>
+      </c>
+      <c r="C175" s="13">
+        <v>10194440</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2118" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66061B69-FD50-4283-9332-66A9BC3ABADC}"/>
+  <xr:revisionPtr revIDLastSave="2128" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E270078D-63A8-4333-AD60-8A3484B7D71D}"/>
   <bookViews>
-    <workbookView xWindow="14364" yWindow="1356" windowWidth="8676" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14436" yWindow="1104" windowWidth="8604" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="114">
   <si>
     <t>Market</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>102.8, -0.0, -2.8</t>
+  </si>
+  <si>
+    <t>15.49, 20.06, 64.45</t>
   </si>
 </sst>
 </file>
@@ -6806,6 +6809,13 @@
         <v>1</v>
       </c>
       <c r="C351" s="10"/>
+      <c r="D351" s="10">
+        <v>46142</v>
+      </c>
+      <c r="E351" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F351" s="10"/>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="6">
@@ -6818,8 +6828,18 @@
         <f>B352/B356</f>
         <v>0.66215495281330328</v>
       </c>
-    </row>
-    <row r="353" spans="1:3">
+      <c r="D352" s="6">
+        <v>2</v>
+      </c>
+      <c r="E352" s="8">
+        <v>4422385</v>
+      </c>
+      <c r="F352" s="7">
+        <f>E352/E356</f>
+        <v>0.65527396275843064</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353" s="6">
         <v>3</v>
       </c>
@@ -6830,8 +6850,18 @@
         <f>B353/B356</f>
         <v>0.22741147153671049</v>
       </c>
-    </row>
-    <row r="354" spans="1:3">
+      <c r="D353" s="6">
+        <v>3</v>
+      </c>
+      <c r="E353" s="8">
+        <v>1534325</v>
+      </c>
+      <c r="F353" s="7">
+        <f>E353/E356</f>
+        <v>0.22734411927259365</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354" s="6">
         <v>1</v>
       </c>
@@ -6842,8 +6872,18 @@
         <f>B354/B356</f>
         <v>6.2226854884837361E-2</v>
       </c>
-    </row>
-    <row r="355" spans="1:3">
+      <c r="D354" s="6">
+        <v>1</v>
+      </c>
+      <c r="E354" s="8">
+        <v>447700</v>
+      </c>
+      <c r="F354" s="7">
+        <f>E354/E356</f>
+        <v>6.6336638064517089E-2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355" s="6">
         <v>4</v>
       </c>
@@ -6854,14 +6894,32 @@
         <f>B355/B356</f>
         <v>4.8206720765148897E-2</v>
       </c>
-    </row>
-    <row r="356" spans="1:3">
+      <c r="D355" s="6">
+        <v>4</v>
+      </c>
+      <c r="E355" s="8">
+        <v>344500</v>
+      </c>
+      <c r="F355" s="7">
+        <f>E355/E356</f>
+        <v>5.1045279904458646E-2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
       <c r="B356" s="9">
         <f>SUM(B352:B355)</f>
         <v>6494945</v>
       </c>
       <c r="C356" s="7">
         <f>SUM(C352:C355)</f>
+        <v>1</v>
+      </c>
+      <c r="E356" s="9">
+        <f>SUM(E352:E355)</f>
+        <v>6748910</v>
+      </c>
+      <c r="F356" s="7">
+        <f>SUM(F352:F355)</f>
         <v>1</v>
       </c>
     </row>
@@ -9299,6 +9357,15 @@
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D173" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="174" spans="1:6" ht="43.2">
       <c r="A174" s="2">
@@ -9309,6 +9376,15 @@
       </c>
       <c r="C174" s="3" t="s">
         <v>111</v>
+      </c>
+      <c r="D174" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -9318,6 +9394,13 @@
       </c>
       <c r="C175" s="13">
         <v>10194440</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="4">
+        <v>-315150</v>
+      </c>
+      <c r="F175" s="13">
+        <v>10338040</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2128" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E270078D-63A8-4333-AD60-8A3484B7D71D}"/>
+  <xr:revisionPtr revIDLastSave="2156" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDA8441-75ED-4CF3-8394-03AFF8C7BC7C}"/>
   <bookViews>
-    <workbookView xWindow="14436" yWindow="1104" windowWidth="8604" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13908" yWindow="1092" windowWidth="10548" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="116">
   <si>
     <t>Market</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>15.49, 20.06, 64.45</t>
+  </si>
+  <si>
+    <t>15.38, 19.92, 64.7</t>
+  </si>
+  <si>
+    <t>102.47, -0.0, -2.47</t>
   </si>
 </sst>
 </file>
@@ -504,6 +510,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -803,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F356"/>
+  <dimension ref="A1:F363"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -6923,6 +6933,128 @@
         <v>1</v>
       </c>
     </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="10">
+        <v>46171</v>
+      </c>
+      <c r="B358" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C358" s="10"/>
+      <c r="D358" s="10">
+        <v>46203</v>
+      </c>
+      <c r="E358" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F358" s="10"/>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="6">
+        <v>2</v>
+      </c>
+      <c r="B359" s="8">
+        <v>4391705</v>
+      </c>
+      <c r="C359" s="7">
+        <f>B359/B363</f>
+        <v>0.65428891954625767</v>
+      </c>
+      <c r="D359" s="6">
+        <v>2</v>
+      </c>
+      <c r="E359" s="8">
+        <v>4704470</v>
+      </c>
+      <c r="F359" s="7">
+        <f>E359/E363</f>
+        <v>0.66851589094218777</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="6">
+        <v>3</v>
+      </c>
+      <c r="B360" s="8">
+        <v>1553915</v>
+      </c>
+      <c r="C360" s="7">
+        <f>B360/B363</f>
+        <v>0.23150675339457524</v>
+      </c>
+      <c r="D360" s="6">
+        <v>3</v>
+      </c>
+      <c r="E360" s="8">
+        <v>1578915</v>
+      </c>
+      <c r="F360" s="7">
+        <f>E360/E363</f>
+        <v>0.2243674139588486</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="6">
+        <v>1</v>
+      </c>
+      <c r="B361" s="8">
+        <v>435600</v>
+      </c>
+      <c r="C361" s="7">
+        <f>B361/B363</f>
+        <v>6.4896948532369519E-2</v>
+      </c>
+      <c r="D361" s="6">
+        <v>1</v>
+      </c>
+      <c r="E361" s="8">
+        <v>428200</v>
+      </c>
+      <c r="F361" s="7">
+        <f>E361/E363</f>
+        <v>6.084819427086257E-2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="6">
+        <v>4</v>
+      </c>
+      <c r="B362" s="8">
+        <v>330960</v>
+      </c>
+      <c r="C362" s="7">
+        <f>B362/B363</f>
+        <v>4.9307378526797556E-2</v>
+      </c>
+      <c r="D362" s="6">
+        <v>4</v>
+      </c>
+      <c r="E362" s="8">
+        <v>325600</v>
+      </c>
+      <c r="F362" s="7">
+        <f>E362/E363</f>
+        <v>4.6268500828101009E-2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="B363" s="9">
+        <f>SUM(B359:B362)</f>
+        <v>6712180</v>
+      </c>
+      <c r="C363" s="7">
+        <f>SUM(C359:C362)</f>
+        <v>1</v>
+      </c>
+      <c r="E363" s="9">
+        <f>SUM(E359:E362)</f>
+        <v>7037185</v>
+      </c>
+      <c r="F363" s="7">
+        <f>SUM(F359:F362)</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6930,7 +7062,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -9367,12 +9499,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="43.2">
+    <row r="174" spans="1:6" ht="57.6">
       <c r="A174" s="2">
         <v>46108</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>111</v>
@@ -9401,6 +9533,62 @@
       </c>
       <c r="F175" s="13">
         <v>10338040</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="57.6">
+      <c r="A178" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D178" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="5"/>
+      <c r="B179" s="4">
+        <v>-316324</v>
+      </c>
+      <c r="C179" s="13">
+        <v>10410540</v>
+      </c>
+      <c r="D179" s="5"/>
+      <c r="E179" s="4">
+        <v>-316324</v>
+      </c>
+      <c r="F179" s="13">
+        <v>10410540</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2156" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDA8441-75ED-4CF3-8394-03AFF8C7BC7C}"/>
+  <xr:revisionPtr revIDLastSave="2164" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5897C9CE-5303-4FA0-84F3-39E9960E9DCC}"/>
   <bookViews>
-    <workbookView xWindow="13908" yWindow="1092" windowWidth="10548" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14076" yWindow="468" windowWidth="8964" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="116">
   <si>
     <t>Market</t>
   </si>
@@ -510,10 +510,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -813,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F363"/>
+  <dimension ref="A1:F370"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -7055,6 +7051,73 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="10">
+        <v>46234</v>
+      </c>
+      <c r="B365" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C365" s="10"/>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="6">
+        <v>2</v>
+      </c>
+      <c r="B366" s="8">
+        <v>4885850</v>
+      </c>
+      <c r="C366" s="7">
+        <f>B366/B370</f>
+        <v>0.65588305968235816</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="6">
+        <v>3</v>
+      </c>
+      <c r="B367" s="8">
+        <v>1739400</v>
+      </c>
+      <c r="C367" s="7">
+        <f>B367/B370</f>
+        <v>0.23349938987310165</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="6">
+        <v>1</v>
+      </c>
+      <c r="B368" s="8">
+        <v>477900</v>
+      </c>
+      <c r="C368" s="7">
+        <f>B368/B370</f>
+        <v>6.4153937231433422E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" s="6">
+        <v>4</v>
+      </c>
+      <c r="B369" s="8">
+        <v>346120</v>
+      </c>
+      <c r="C369" s="7">
+        <f>B369/B370</f>
+        <v>4.646361321310679E-2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="B370" s="9">
+        <f>SUM(B366:B369)</f>
+        <v>7449270</v>
+      </c>
+      <c r="C370" s="7">
+        <f>SUM(C366:C369)</f>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7062,7 +7125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -9591,6 +9654,37 @@
         <v>10410540</v>
       </c>
     </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="57.6">
+      <c r="A182" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="5"/>
+      <c r="B183" s="4">
+        <v>-316324</v>
+      </c>
+      <c r="C183" s="13">
+        <v>10410540</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
